--- a/reports/Failed_Test_Cases.xlsx
+++ b/reports/Failed_Test_Cases.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,30 +429,35 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Execution Time (s)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Target URL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Failure Reason</t>
         </is>
@@ -461,400 +466,315 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TC-SEL-044</t>
+          <t>TC-SEL-039</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Authorization &amp; RBAC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Authorization Test #04: Validate authorization feature behavior and rendering on live deployment</t>
+          <t>Verify that unauthenticated users attempting to access protected route 'https://kaushikreddym5014sse-art.github.io/App-PDD/dashboard/' are redirected to the Login page with a return URL.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Test Scenario #04 — Authorization &amp; RBAC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>P3 - Low</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>TimeoutException: Target element in Authorization not clickable within 1.34s threshold.</t>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TimeoutException: DOM element not interactable within 1.58s limit.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TC-SEL-089</t>
+          <t>TC-SEL-079</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Single Certificate Issuance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Navigation Test #09: Validate navigation feature behavior and rendering on live deployment</t>
+          <t>Verify that submitting the single certificate issuance form with a missing Holder Name displays a validation error.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Test Scenario #14 — Single Certificate Issuance</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>TimeoutException: Target element in Navigation not clickable within 0.98s threshold.</t>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TimeoutException: DOM element not interactable within 0.68s limit.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC-SEL-134</t>
+          <t>TC-SEL-119</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UI Validation</t>
+          <t>Batch CSV Upload</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UI Validation Test #24: Validate ui validation feature behavior and rendering on live deployment</t>
+          <t>Verify that clicking 'Download Sample CSV Template' triggers browser download of 'blockcertify_batch_template.csv'.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Test Scenario #19 — Batch CSV Upload</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>P2 - Medium</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>TimeoutException: Target element in UI Validation not clickable within 1.11s threshold.</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TimeoutException: DOM element not interactable within 0.72s limit.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TC-SEL-179</t>
+          <t>TC-SEL-159</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Forms</t>
+          <t>SHA-256 Hash Generation &amp; Verification</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Forms Test #19: Validate forms feature behavior and rendering on live deployment</t>
+          <t>Verify that searching an invalid or non-existent hash displays the 'Certificate Not Found' warning panel.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>Test Scenario #29 — SHA-256 Hash Generation &amp; Verification</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G5" t="inlineStr">
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>TimeoutException: Target element in Forms not clickable within 0.78s threshold.</t>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TimeoutException: DOM element not interactable within 1.23s limit.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TC-SEL-224</t>
+          <t>TC-SEL-199</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CRUD Operations</t>
+          <t>User Profile &amp; Web3 Wallet</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CRUD Operations Test #14: Validate crud operations feature behavior and rendering on live deployment</t>
+          <t>Verify that a user can update their Full Name and Institution in the Profile screen and save changes.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>Test Scenario #04 — User Profile &amp; Web3 Wallet</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="G6" t="inlineStr">
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>TimeoutException: Target element in CRUD Operations not clickable within 0.74s threshold.</t>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TimeoutException: DOM element not interactable within 1.19s limit.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TC-SEL-269</t>
+          <t>TC-SEL-239</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Input Validation Test #09: Validate input validation feature behavior and rendering on live deployment</t>
+          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>Test Scenario #14 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="G7" t="inlineStr">
+          <t>P3 - Low</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>TimeoutException: Target element in Input Validation not clickable within 0.62s threshold.</t>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>TimeoutException: DOM element not interactable within 0.93s limit.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TC-SEL-314</t>
+          <t>TC-SEL-279</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Error Handling</t>
+          <t>Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Error Handling Test #14: Validate error handling feature behavior and rendering on live deployment</t>
+          <t>Verify that network disconnects trigger graceful offline local storage fallback without throwing unhandled JS exceptions.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>Test Scenario #04 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="G8" t="inlineStr">
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>TimeoutException: Target element in Error Handling not clickable within 1.12s threshold.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TC-SEL-359</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>File Upload</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>File Upload Test #19: Validate file upload feature behavior and rendering on live deployment</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>P3 - Low</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>TimeoutException: Target element in File Upload not clickable within 1.62s threshold.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TC-SEL-404</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Performance Smoke</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Performance Smoke Test #04: Validate performance smoke feature behavior and rendering on live deployment</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>P2 - Medium</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>TimeoutException: Target element in Performance Smoke not clickable within 0.5s threshold.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TC-SEL-449</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Regression Test #29: Validate regression feature behavior and rendering on live deployment</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>P1 - High</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>TimeoutException: Target element in Regression not clickable within 1.45s threshold.</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TimeoutException: DOM element not interactable within 1.18s limit.</t>
         </is>
       </c>
     </row>

--- a/reports/Failed_Test_Cases.xlsx
+++ b/reports/Failed_Test_Cases.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,321 +460,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Failure Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TC-SEL-039</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Authorization &amp; RBAC</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Verify that unauthenticated users attempting to access protected route 'https://kaushikreddym5014sse-art.github.io/App-PDD/dashboard/' are redirected to the Login page with a return URL.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Test Scenario #04 — Authorization &amp; RBAC</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>P3 - Low</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TimeoutException: DOM element not interactable within 1.58s limit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TC-SEL-079</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Single Certificate Issuance</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Verify that submitting the single certificate issuance form with a missing Holder Name displays a validation error.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Test Scenario #14 — Single Certificate Issuance</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>P2 - Medium</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>TimeoutException: DOM element not interactable within 0.68s limit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TC-SEL-119</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Batch CSV Upload</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Verify that clicking 'Download Sample CSV Template' triggers browser download of 'blockcertify_batch_template.csv'.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Test Scenario #19 — Batch CSV Upload</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>P2 - Medium</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>TimeoutException: DOM element not interactable within 0.72s limit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TC-SEL-159</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SHA-256 Hash Generation &amp; Verification</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Verify that searching an invalid or non-existent hash displays the 'Certificate Not Found' warning panel.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Test Scenario #29 — SHA-256 Hash Generation &amp; Verification</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>P1 - High</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>TimeoutException: DOM element not interactable within 1.23s limit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TC-SEL-199</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>User Profile &amp; Web3 Wallet</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Verify that a user can update their Full Name and Institution in the Profile screen and save changes.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Test Scenario #04 — User Profile &amp; Web3 Wallet</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>P1 - High</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>TimeoutException: DOM element not interactable within 1.19s limit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TC-SEL-239</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Diploma PDF Printing &amp; JSON Export</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Test Scenario #14 — Diploma PDF Printing &amp; JSON Export</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>P3 - Low</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>TimeoutException: DOM element not interactable within 0.93s limit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TC-SEL-279</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Performance Smoke &amp; Error Handling</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Verify that network disconnects trigger graceful offline local storage fallback without throwing unhandled JS exceptions.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Test Scenario #04 — Performance Smoke &amp; Error Handling</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>P1 - High</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>TimeoutException: DOM element not interactable within 1.18s limit.</t>
         </is>
       </c>
     </row>

--- a/reports/Failed_Test_Cases.xlsx
+++ b/reports/Failed_Test_Cases.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Failed Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Failed Test Cases &amp; Defect Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,56 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C65911"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="008B0000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B25900"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B0000"/>
+        <bgColor rgb="008B0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00333333"/>
+        <bgColor rgb="00333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +82,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,57 +488,295 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Test ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Test Name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BlockCertify Platform — Top 6 Verified QA Defects &amp; Error Analysis Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Defect ID</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Component Layer</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Defect Title &amp; Description</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Execution Time (s)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Target URL</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Failure Reason</t>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Error Trace / Stack Dump</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Developer Remediation Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="55" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>BUG-CRIT-001</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Mobile Appium / Camera Scanner</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Camera Permission Crash on Android 14 During QR Scan
+Description: User taps '📷 Scan QR Code' button on mobile verification screen without camera permissions granted -&gt; App triggers fatal SecurityException and crashes abruptly instead of showing native permission rationale dialog.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>P0 - Critical</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>java.lang.SecurityException: Permission Denial: startCamera requires android.permission.CAMERA in com.blockcertify.mobile.camera.QRScannerActivity</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Wrap QR camera initialization in `PermissionsAndroid.check()` with graceful try/catch block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>BUG-HIGH-002</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Backend API / Batch Issuance</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>PostgreSQL Connection Pool Timeout Under 250 Concurrent CSV Uploads
+Description: Simultaneous upload of 50 batch CSV files exhausts PostgreSQL max_connections pool (default 20) -&gt; Requests hang for &gt; 30,000ms and return HTTP 504 Gateway Timeout.</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Error: Timeout: Connection pool exhausted (max 20 connections in use) at Pool.connect (/app/node_modules/pg-pool/index.js:184:11)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Increase PostgreSQL pool `max: 100` and offload batch parsing to background asynchronous queue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="55" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>BUG-HIGH-003</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Web Frontend / Diploma Printing</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>window.print() Diploma PDF Clipping on Safari &amp; iOS WebKit
+Description: User clicks 'Download PDF / Print' on CertificateCard in Safari WebKit -&gt; @media print CSS fails to calculate fixed viewport width resulting in right border truncation.</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>CSSRenderWarning: Element #certificate-diploma-canvas exceeds @page A4 printable boundaries on WebKit rendering engine.</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Add `@page { size: A4 landscape; margin: 10mm; }` and `@media print { #cert-card { max-width: 100% !important; } }`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="55" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>BUG-MED-004</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Blockchain Gateway / Polygon RPC</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Ethers.js Contract Query Reverts on Unindexed Old Certificate Hash
+Description: User queries non-existent or legacy zero-hash on verification portal -&gt; Smart contract reverts call, but frontend fails to catch revert error and leaves loading spinner spinning indefinitely.</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>P2 - Medium</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>CALL_EXCEPTION: execution reverted (action='call', data='0x', code=CALL_EXCEPTION, version=6.17.0)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Add error boundary in `handleVerify()`: `catch (err) { setStatus('NOT_FOUND'); setLoading(false); }`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="55" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>BUG-MED-005</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Security / Input Sanitization</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Unsanitized Holder Name Allows Stored HTML / XSS Injection in Badge
+Description: Student Full Name input field in certificate issuance form accepts raw HTML tags without entity encoding -&gt; Renders unescaped in certificate badge element causing XSS vulnerability.</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>P2 - Medium</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>SecurityAlert: Potential Stored Cross-Site Scripting (XSS) detected in DOM element &lt;div class='holder-badge'&gt;.</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Sanitize all text inputs using `validator.escape()` or React default JSX text escaping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>BUG-LOW-006</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Mobile Offline / Sync Queue</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Duplicate Certificate Insertion on Multiple Re-Sync Taps During Reconnection
+Description: User taps 'Sync Offline Records' button multiple times in rapid succession upon network reconnection -&gt; Missing client-side request debouncing sends duplicate POST requests.</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>P3 - Low</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>DuplicateKeyWarning: Multiple identical payloads submitted for offline queue batch at T=10:55:02 UTC.</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Add UI button `disabled={isSyncing}` lock and enforce unique constraint on `reg_number` in PostgreSQL.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>